--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484262_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484262_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4988</v>
+        <v>7.2124</v>
       </c>
       <c r="E2" t="n">
-        <v>5.48</v>
+        <v>5.7335</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0188</v>
+        <v>1.4789</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1494</v>
+        <v>3.3515</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2039</v>
+        <v>3.8378</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0545</v>
+        <v>-0.4864</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5642</v>
+        <v>4.7806</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4833</v>
+        <v>4.0522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0809</v>
+        <v>0.7284</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4148</v>
+        <v>-1.4291</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2793</v>
+        <v>-0.2144</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1354</v>
+        <v>-1.2148</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3261</v>
+        <v>1.205</v>
       </c>
       <c r="T2" t="n">
-        <v>0.432</v>
+        <v>0.8365</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8941</v>
+        <v>0.3686</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8279</v>
+        <v>3.0466</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4373</v>
+        <v>3.0466</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4303</v>
+        <v>6.9836</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7335</v>
+        <v>5.2372</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6968</v>
+        <v>1.7464</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3515</v>
+        <v>4.1494</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8378</v>
+        <v>4.2039</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4864</v>
+        <v>-0.0545</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7806</v>
+        <v>4.5642</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0522</v>
+        <v>4.4833</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7284</v>
+        <v>0.0809</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4291</v>
+        <v>-0.4148</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2144</v>
+        <v>-0.2793</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2148</v>
+        <v>-0.1354</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4229</v>
+        <v>0.8109</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8365</v>
+        <v>0.1892</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5864</v>
+        <v>0.6217</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0466</v>
+        <v>1.8279</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0466</v>
+        <v>2.4373</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5832</v>
+        <v>6.4194</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8106</v>
+        <v>4.15</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7726</v>
+        <v>2.2694</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8493</v>
+        <v>3.2811</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3625</v>
+        <v>0.6646</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5132</v>
+        <v>2.6165</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1345</v>
+        <v>3.6308</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6467</v>
+        <v>1.1486</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5122</v>
+        <v>2.4822</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2852</v>
+        <v>-0.3498</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2842</v>
+        <v>-0.484</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.001</v>
+        <v>0.1342</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7339</v>
+        <v>0.7477</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1337</v>
+        <v>0.2773</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6002</v>
+        <v>0.4704</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.587</v>
+        <v>6.1321</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6444</v>
+        <v>3.305</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9426</v>
+        <v>2.8271</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2811</v>
+        <v>2.8493</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6646</v>
+        <v>3.3625</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6165</v>
+        <v>-0.5132</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6308</v>
+        <v>3.1345</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1486</v>
+        <v>3.6467</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4822</v>
+        <v>-0.5122</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3498</v>
+        <v>-0.2852</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.484</v>
+        <v>-0.2842</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1342</v>
+        <v>-0.001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0847</v>
+        <v>1.2828</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2283</v>
+        <v>0.6281</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1436</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.1879</v>
+        <v>5.3939</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2393</v>
+        <v>3.7449</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9486</v>
+        <v>1.649</v>
       </c>
       <c r="G6" t="n">
         <v>1.8527</v>
@@ -922,13 +922,13 @@
         <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8897</v>
+        <v>1.0957</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.154</v>
+        <v>0.3516</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0437</v>
+        <v>0.7441</v>
       </c>
       <c r="V6" t="n">
         <v>1.2735</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0864</v>
+        <v>3.3159</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2499</v>
+        <v>1.4521</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8365</v>
+        <v>1.8638</v>
       </c>
       <c r="G7" t="n">
         <v>1.3982</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1254</v>
+        <v>0.3549</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3631</v>
+        <v>-0.1609</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4886</v>
+        <v>0.5158</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4283</v>
+        <v>2.9616</v>
       </c>
       <c r="E8" t="n">
-        <v>1.984</v>
+        <v>2.4084</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4442</v>
+        <v>0.5532</v>
       </c>
       <c r="G8" t="n">
         <v>1.8439</v>
@@ -1078,13 +1078,13 @@
         <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1937</v>
+        <v>0.727</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.3447</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2734</v>
+        <v>0.3823</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0667</v>
+        <v>2.2033</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7081</v>
+        <v>2.6269</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6414</v>
+        <v>-0.4235</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6454</v>
@@ -1156,13 +1156,13 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5167</v>
+        <v>0.6534</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3385</v>
+        <v>0.2573</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1782</v>
+        <v>0.3961</v>
       </c>
       <c r="V9" t="n">
         <v>2.4373</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6374</v>
+        <v>1.4878</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1272</v>
+        <v>-0.1678</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7646</v>
+        <v>1.6556</v>
       </c>
       <c r="G10" t="n">
         <v>0.2392</v>
@@ -1234,13 +1234,13 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8903</v>
+        <v>0.7408</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3247</v>
+        <v>0.2841</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5656</v>
+        <v>0.4566</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6642</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.0425</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.1205</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8403</v>
+        <v>0.922</v>
       </c>
       <c r="G11" t="n">
         <v>0.9524</v>
@@ -1312,13 +1312,13 @@
         <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.115</v>
+        <v>0.3989</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1624</v>
+        <v>0.3646</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0474</v>
+        <v>0.0343</v>
       </c>
       <c r="V11" t="n">
         <v>0.2772</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>I. MACÍAS MERINO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1368</v>
+        <v>0.2831</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9683</v>
+        <v>-0.4518</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1051</v>
+        <v>0.7349</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.197</v>
+        <v>-0.659</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3413</v>
+        <v>-0.6994</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5383</v>
+        <v>0.0405</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3155</v>
+        <v>0.2951</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2346</v>
+        <v>-0.2853</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>0.5803</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5125</v>
+        <v>-0.954</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8933</v>
+        <v>-0.4142</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6192</v>
+        <v>-0.5399</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5644</v>
+        <v>0.4732</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9383</v>
+        <v>0.2298</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6261</v>
+        <v>0.2434</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3321</v>
+        <v>0.6642</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2308</v>
+        <v>-0.9336</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7751</v>
+        <v>0.2804</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5443</v>
+        <v>-1.214</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.659</v>
+        <v>-0.197</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6994</v>
+        <v>1.3413</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0405</v>
+        <v>-1.5383</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2951</v>
+        <v>2.3155</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2853</v>
+        <v>2.2346</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5803</v>
+        <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.954</v>
+        <v>-2.5125</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4142</v>
+        <v>-0.8933</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5399</v>
+        <v>-1.6192</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
         <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0407</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0935</v>
+        <v>0.2504</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0528</v>
+        <v>0.5172</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6642</v>
+        <v>-0.3321</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>41.897</v>
+        <v>42.502</v>
       </c>
       <c r="E14" t="n">
-        <v>27.8341</v>
+        <v>28.4393</v>
       </c>
       <c r="F14" t="n">
         <v>14.0628</v>
@@ -1531,7 +1531,7 @@
         <v>-13.6395</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.1902</v>
+        <v>-4.190200000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-9.449399999999999</v>
@@ -1546,13 +1546,13 @@
         <v>22.4646</v>
       </c>
       <c r="S14" t="n">
-        <v>8.652700000000001</v>
+        <v>9.257899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.247499999999999</v>
+        <v>3.8527</v>
       </c>
       <c r="U14" t="n">
-        <v>5.405300000000001</v>
+        <v>5.405200000000001</v>
       </c>
       <c r="V14" t="n">
         <v>10.9676</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0142</v>
+        <v>1.6209</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7364</v>
+        <v>3.9386</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7222</v>
+        <v>-2.3177</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0173</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1721</v>
+        <v>-0.5654</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8198</v>
+        <v>-0.6175</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3523</v>
+        <v>0.0522</v>
       </c>
       <c r="V15" t="n">
         <v>0.0549</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.0727</v>
+        <v>-2.9379</v>
       </c>
       <c r="E16" t="n">
         <v>-2.6913</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3814</v>
+        <v>-0.2466</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2914</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7814</v>
+        <v>-0.6466</v>
       </c>
       <c r="T16" t="n">
         <v>-0.9078000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1265</v>
+        <v>0.2613</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.0887</v>
+        <v>-4.23</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8526</v>
+        <v>-1.156</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2361</v>
+        <v>-3.074</v>
       </c>
       <c r="G17" t="n">
         <v>-3.4394</v>
@@ -1780,13 +1780,13 @@
         <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2707</v>
+        <v>-0.412</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.341</v>
+        <v>-0.6444</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0703</v>
+        <v>0.2324</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5507</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.9816</v>
+        <v>-4.6731</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6171</v>
+        <v>-2.4149</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3645</v>
+        <v>-2.2583</v>
       </c>
       <c r="G18" t="n">
         <v>-1.978</v>
@@ -1858,13 +1858,13 @@
         <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6482</v>
+        <v>-0.3398</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4704</v>
+        <v>-0.2682</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1778</v>
+        <v>-0.0716</v>
       </c>
       <c r="V18" t="n">
         <v>-2.16</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1669</v>
+        <v>-4.7753</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0577</v>
+        <v>-0.1446</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.2245</v>
+        <v>-4.6308</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2773</v>
@@ -1936,13 +1936,13 @@
         <v>3.1255</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3035</v>
+        <v>-0.912</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4483</v>
+        <v>-0.6505</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.2615</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8279</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.3614</v>
+        <v>-4.9634</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8771</v>
+        <v>-3.776</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4843</v>
+        <v>-1.1874</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0492</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1401</v>
+        <v>-0.7421</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.652</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4881</v>
+        <v>-0.1913</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8069</v>
+        <v>-5.497</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4369</v>
+        <v>-2.2347</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3699</v>
+        <v>-3.2623</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7767</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9949</v>
+        <v>-0.6851</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6657</v>
+        <v>-0.4635</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3291</v>
+        <v>-0.2215</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8865</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1501</v>
+        <v>-6.826</v>
       </c>
       <c r="E22" t="n">
         <v>-2.667</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.4831</v>
+        <v>-4.1589</v>
       </c>
       <c r="G22" t="n">
         <v>-3.64</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9129</v>
+        <v>-0.5887</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4099</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.503</v>
+        <v>-0.1789</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3787</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2828</v>
+        <v>-6.9185</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7146</v>
+        <v>-2.9168</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5682</v>
+        <v>-4.0017</v>
       </c>
       <c r="G23" t="n">
         <v>0.053</v>
@@ -2248,13 +2248,13 @@
         <v>3.1255</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.429</v>
+        <v>-1.0647</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6904</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7386</v>
+        <v>-0.1721</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2186</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-41.8969</v>
+        <v>-39.20030000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.0625</v>
+        <v>-14.0627</v>
       </c>
       <c r="F24" t="n">
-        <v>-27.8342</v>
+        <v>-25.1377</v>
       </c>
       <c r="G24" t="n">
         <v>-16.4163</v>
@@ -2326,13 +2326,13 @@
         <v>16.6043</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.652799999999999</v>
+        <v>-5.9564</v>
       </c>
       <c r="T24" t="n">
         <v>-5.4053</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.2474</v>
+        <v>-0.5509999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-10.9675</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484262_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484262_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9616</v>
+        <v>2.2033</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4084</v>
+        <v>2.6269</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5532</v>
+        <v>-0.4235</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8439</v>
+        <v>-2.6454</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2507</v>
+        <v>-0.5815</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5931999999999999</v>
+        <v>-2.0639</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0172</v>
+        <v>-0.0677</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5349</v>
+        <v>-0.1625</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4822</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1733</v>
+        <v>-2.5777</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2842</v>
+        <v>-0.419</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8891</v>
+        <v>-2.1587</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>0.727</v>
+        <v>0.6534</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3447</v>
+        <v>0.2573</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3823</v>
+        <v>0.3961</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1151,72 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2033</v>
+        <v>1.8349</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6269</v>
+        <v>1.8349</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4235</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6454</v>
+        <v>1.8349</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5815</v>
+        <v>1.2279</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0639</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0677</v>
+        <v>1.8349</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1625</v>
+        <v>1.2279</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5777</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.419</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1587</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6534</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2573</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3961</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0425</v>
+        <v>1.1267</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1205</v>
+        <v>0.5735</v>
       </c>
       <c r="F11" t="n">
-        <v>0.922</v>
+        <v>0.5532</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9524</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5866</v>
+        <v>0.0228</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6342</v>
+        <v>-0.0138</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4321</v>
+        <v>2.1822</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3917</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>1.8752</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4797</v>
+        <v>-2.1733</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1949</v>
+        <v>-0.2842</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6747</v>
+        <v>-1.8891</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3989</v>
+        <v>0.727</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3646</v>
+        <v>0.3447</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0343</v>
+        <v>0.3823</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2831</v>
+        <v>1.0425</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4518</v>
+        <v>0.1205</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7349</v>
+        <v>0.922</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.659</v>
+        <v>0.9524</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6994</v>
+        <v>1.5866</v>
       </c>
       <c r="I12" t="n">
+        <v>-0.6342</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.4321</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.3917</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.0405</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.2951</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.2853</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.5803</v>
-      </c>
       <c r="M12" t="n">
-        <v>-0.954</v>
+        <v>-0.4797</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4142</v>
+        <v>0.1949</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5399</v>
+        <v>-0.6747</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4732</v>
+        <v>0.3989</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2298</v>
+        <v>0.3646</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2434</v>
+        <v>0.0343</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>I. MACÍAS MERINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9336</v>
+        <v>0.307</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2804</v>
+        <v>0.307</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.197</v>
+        <v>0.307</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3413</v>
+        <v>0.307</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5383</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3155</v>
+        <v>0.307</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2346</v>
+        <v>0.307</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5125</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8933</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6192</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7675999999999999</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2504</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5172</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MACIAS MERINO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,229 +1566,240 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>42.502</v>
+        <v>-0.0239</v>
       </c>
       <c r="E14" t="n">
-        <v>28.4393</v>
+        <v>-0.7588</v>
       </c>
       <c r="F14" t="n">
-        <v>14.0628</v>
+        <v>0.7349</v>
       </c>
       <c r="G14" t="n">
-        <v>16.4163</v>
+        <v>-0.9659</v>
       </c>
       <c r="H14" t="n">
-        <v>18.4434</v>
+        <v>-1.0064</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.0271</v>
+        <v>0.0405</v>
       </c>
       <c r="J14" t="n">
-        <v>30.0557</v>
+        <v>-0.0119</v>
       </c>
       <c r="K14" t="n">
-        <v>22.6337</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>7.4219</v>
+        <v>0.5803</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.6395</v>
+        <v>-0.954</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.190200000000001</v>
+        <v>-0.4142</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.449399999999999</v>
+        <v>-0.5399</v>
       </c>
       <c r="P14" t="n">
-        <v>5.860399999999998</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.6039</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>22.4646</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>9.257899999999999</v>
+        <v>0.4732</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8527</v>
+        <v>0.2298</v>
       </c>
       <c r="U14" t="n">
-        <v>5.405200000000001</v>
+        <v>0.2434</v>
       </c>
       <c r="V14" t="n">
-        <v>10.9676</v>
+        <v>0.6642</v>
       </c>
       <c r="W14" t="n">
-        <v>11.1352</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1674</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6209</v>
+        <v>-0.9336</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9386</v>
+        <v>0.2804</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3177</v>
+        <v>-1.214</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0173</v>
+        <v>-0.197</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.3359</v>
+        <v>1.3413</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3186</v>
+        <v>-1.5383</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5562</v>
+        <v>2.3155</v>
       </c>
       <c r="K15" t="n">
-        <v>0.023</v>
+        <v>2.2346</v>
       </c>
       <c r="L15" t="n">
-        <v>4.5331</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.5735</v>
+        <v>-2.5125</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.3589</v>
+        <v>-0.8933</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2146</v>
+        <v>-1.6192</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5654</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6175</v>
+        <v>0.2504</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0522</v>
+        <v>0.5172</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0549</v>
+        <v>-0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.9379</v>
+        <v>42.50200000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.6913</v>
+        <v>28.4393</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2466</v>
+        <v>14.0628</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2914</v>
+        <v>16.4164</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9949</v>
+        <v>18.4434</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2965</v>
+        <v>-2.0271</v>
       </c>
       <c r="J16" t="n">
-        <v>0.17</v>
+        <v>30.0556</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0614</v>
+        <v>22.6338</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1086</v>
+        <v>7.4219</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4613</v>
+        <v>-13.6395</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0563</v>
+        <v>-4.190200000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4051</v>
+        <v>-9.449400000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.8604</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-16.6039</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>22.4646</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6466</v>
+        <v>9.257900000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9078000000000001</v>
+        <v>3.8527</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2613</v>
+        <v>5.405200000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>10.9676</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>11.1352</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1674</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.23</v>
+        <v>1.6209</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.156</v>
+        <v>3.9386</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.074</v>
+        <v>-2.3177</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.4394</v>
+        <v>-0.0173</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8347</v>
+        <v>-3.3359</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6046</v>
+        <v>3.3186</v>
       </c>
       <c r="J17" t="n">
-        <v>0.52</v>
+        <v>4.5562</v>
       </c>
       <c r="K17" t="n">
-        <v>1.045</v>
+        <v>0.023</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5251</v>
+        <v>4.5331</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.9593</v>
+        <v>-4.5735</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.8798</v>
+        <v>-3.3589</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0795</v>
+        <v>-1.2146</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.412</v>
+        <v>-0.5654</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6444</v>
+        <v>-0.6175</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2324</v>
+        <v>0.0522</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5507</v>
+        <v>0.0549</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.6731</v>
+        <v>-2.9379</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4149</v>
+        <v>-2.6913</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2583</v>
+        <v>-0.2466</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.978</v>
+        <v>-2.2914</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4498</v>
+        <v>-1.9949</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4718</v>
+        <v>-0.2965</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4705</v>
+        <v>0.17</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6728</v>
+        <v>0.0614</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2023</v>
+        <v>0.1086</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5075</v>
+        <v>-2.4613</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7769</v>
+        <v>-2.0563</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2694</v>
+        <v>-0.4051</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3398</v>
+        <v>-0.6466</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2682</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0716</v>
+        <v>0.2613</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.7753</v>
+        <v>-4.23</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1446</v>
+        <v>-1.156</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.6308</v>
+        <v>-3.074</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2773</v>
+        <v>-3.4394</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5876</v>
+        <v>-1.8347</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3103</v>
+        <v>-1.6046</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7802</v>
+        <v>0.52</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2553</v>
+        <v>1.045</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5249</v>
+        <v>-0.5251</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.0575</v>
+        <v>-3.9593</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.8429</v>
+        <v>-2.8798</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2146</v>
+        <v>-1.0795</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1255</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.912</v>
+        <v>-0.412</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6505</v>
+        <v>-0.6444</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2615</v>
+        <v>0.2324</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>-1.5507</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6093</v>
+        <v>-0.0549</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4373</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9634</v>
+        <v>-4.6731</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.776</v>
+        <v>-2.4149</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1874</v>
+        <v>-2.2583</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0492</v>
+        <v>-1.978</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7705</v>
+        <v>-2.4498</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2787</v>
+        <v>0.4718</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2717</v>
+        <v>-0.4705</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.6728</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3344</v>
+        <v>0.2023</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7775</v>
+        <v>-1.5075</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.7769</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9443</v>
+        <v>0.2694</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7421</v>
+        <v>-0.3398</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.2682</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1913</v>
+        <v>-0.0716</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.497</v>
+        <v>-4.7753</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2347</v>
+        <v>-0.1446</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2623</v>
+        <v>-4.6308</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7767</v>
+        <v>-0.2773</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6012</v>
+        <v>-0.5876</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1755</v>
+        <v>0.3103</v>
       </c>
       <c r="J21" t="n">
-        <v>1.159</v>
+        <v>4.7802</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3901</v>
+        <v>3.2553</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7688</v>
+        <v>1.5249</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9356</v>
+        <v>-5.0575</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9913</v>
+        <v>-3.8429</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9443</v>
+        <v>-1.2146</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1488</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-4.8836</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>3.1255</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6851</v>
+        <v>-0.912</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4635</v>
+        <v>-0.6505</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2215</v>
+        <v>-0.2615</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8865</v>
+        <v>-1.8279</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8865</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.826</v>
+        <v>-4.9634</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.667</v>
+        <v>-3.776</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1589</v>
+        <v>-1.1874</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.64</v>
+        <v>-3.0492</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3318</v>
+        <v>-0.7705</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3081</v>
+        <v>-2.2787</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.593</v>
+        <v>-1.2717</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9594</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.3344</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.047</v>
+        <v>-1.7775</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3725</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6745</v>
+        <v>-0.9443</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5887</v>
+        <v>-0.7421</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4099</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1789</v>
+        <v>-0.1913</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.3787</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9185</v>
+        <v>-5.497</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9168</v>
+        <v>-2.2347</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0017</v>
+        <v>-3.2623</v>
       </c>
       <c r="G23" t="n">
-        <v>0.053</v>
+        <v>-1.7767</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.537</v>
+        <v>-1.6012</v>
       </c>
       <c r="I23" t="n">
-        <v>3.59</v>
+        <v>-0.1755</v>
       </c>
       <c r="J23" t="n">
-        <v>5.7895</v>
+        <v>1.159</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9849</v>
+        <v>0.3901</v>
       </c>
       <c r="L23" t="n">
-        <v>4.8046</v>
+        <v>0.7688</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.7364</v>
+        <v>-2.9356</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.5219</v>
+        <v>-1.9913</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2146</v>
+        <v>-0.9443</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.6882</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.8137</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1255</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0647</v>
+        <v>-0.6851</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-0.4635</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1721</v>
+        <v>-0.2215</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-6.826</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-4.1589</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.3318</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.3081</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.593</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.9594</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.047</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.3725</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.5887</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.4099</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1789</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-3.3787</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E. ZUSTOVICH</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.9185</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.9168</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-4.0017</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.537</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.7895</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.8046</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-5.7364</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-4.5219</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-4.6882</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-7.8137</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.1255</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-1.0647</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.8925999999999999</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1721</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484262_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-39.20030000000001</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>-14.0627</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>-25.1377</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>-16.4163</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>-18.4434</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>2.0273</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>13.6397</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K26" t="n">
         <v>4.1902</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>9.449200000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-30.0556</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-22.6337</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>-7.422099999999999</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>-5.860200000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-22.4643</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>16.6043</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>-5.9564</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-5.4053</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>-0.5509999999999999</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>-10.9675</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>0.1673999999999999</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-11.1352</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
